--- a/base_prov_co/rappi/rappi_abbott_2026_09_30.xlsx
+++ b/base_prov_co/rappi/rappi_abbott_2026_09_30.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rappi" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rappi'!$A$1:$Q$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rappi'!$A$1:$R$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -471,65 +471,70 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>MARCA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>categoría</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seller</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ventas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>valoración</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>reviews</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_count</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_count</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>title_count_characters</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>count_character_desc</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>url_imagen</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>url_producto</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>disponibilidad</t>
         </is>
@@ -556,17 +561,16 @@
           <t>8427030008608</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>Abbott</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>-</t>
@@ -577,34 +581,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>48</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>153</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>- Es un medicamento - No exceder su consumo - Leer las indicaciones y contraindicaciones en la etiqueta - Si los síntomas persisten, consulte a su médico</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>https://images.rappi.com/products/5a562d78-8f6d-49b8-82b8-503224b957a1.png?d=900x750&amp;e=webp&amp;q=30</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>https://www.rappi.com.co/p/ensure-advance-vainilla-con-protein-4720</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -631,17 +640,16 @@
           <t>8710428013859</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Abbott</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>-</t>
@@ -652,34 +660,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>45</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>153</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>- Es un medicamento - No exceder su consumo - Leer las indicaciones y contraindicaciones en la etiqueta - Si los síntomas persisten, consulte a su médico</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>https://images.rappi.com/products/a6e876f0-8058-4c79-b704-79d1c6b4c9e4.png?d=900x750&amp;e=webp&amp;q=30</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>https://www.rappi.com.co/p/ensure-advance-fresa-con-proteina-h-6165</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -706,17 +719,16 @@
           <t>8710428018694</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Abbott</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>-</t>
@@ -727,34 +739,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>51</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>153</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>- Es un medicamento - No exceder su consumo - Leer las indicaciones y contraindicaciones en la etiqueta - Si los síntomas persisten, consulte a su médico</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>https://images.rappi.com/products/109c3727-c472-4801-93f8-991856ea684a.png?d=900x750&amp;e=webp&amp;q=30</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>https://www.rappi.com.co/p/ensure-advance-chocolate-con-protei-2296793</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -781,17 +798,16 @@
           <t>8427030003153</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>Abbott</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>-</t>
@@ -802,34 +818,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>21</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>153</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>- Es un medicamento - No exceder su consumo - Leer las indicaciones y contraindicaciones en la etiqueta - Si los síntomas persisten, consulte a su médico</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>https://images.rappi.com/products/43571137-d473-4dc3-9310-0d17ad83ccc6.png?d=900x750&amp;e=webp&amp;q=30</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>https://www.rappi.com.co/p/ensure-vainilla-polvo-6184</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -856,17 +877,16 @@
           <t>8710428019561</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Abbott</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>-</t>
@@ -877,34 +897,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>41</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>153</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>- Es un medicamento - No exceder su consumo - Leer las indicaciones y contraindicaciones en la etiqueta - Si los síntomas persisten, consulte a su médico</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>https://images.rappi.com/products/258684700252_eergnvotzfmj_950863011957_vxbijreuvqhi_7403_23.png?d=900x750&amp;e=webp&amp;q=30</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>https://www.rappi.com.co/p/ensure-vainilla-liquido-2688828</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -931,17 +956,16 @@
           <t>8427030008936</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>Abbott</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>-</t>
@@ -952,41 +976,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>23</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>153</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>- Es un medicamento - No exceder su consumo - Leer las indicaciones y contraindicaciones en la etiqueta - Si los síntomas persisten, consulte a su médico</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://images.rappi.com/products/512e4e57-d843-4f1f-b6b9-af90ab1f33d0.png?d=900x750&amp;e=webp&amp;q=30</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>https://www.rappi.com.co/p/glucerna-vainilla-polvo-4721</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q7"/>
+  <autoFilter ref="A1:R7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>